--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/172.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/172.xlsx
@@ -426,13 +426,13 @@
         <v>-17.78818047346298</v>
       </c>
       <c r="E2">
-        <v>-0.6386754083793909</v>
+        <v>-3.829107615581365</v>
       </c>
       <c r="F2">
-        <v>-2.372055884553379</v>
+        <v>-1.847720027766362</v>
       </c>
       <c r="G2">
-        <v>-0.6078769014982307</v>
+        <v>-4.720653699118848</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.6873857240549</v>
       </c>
       <c r="E3">
-        <v>-1.160382784907062</v>
+        <v>-4.413511714745232</v>
       </c>
       <c r="F3">
-        <v>-1.680338453621888</v>
+        <v>-1.808746169832048</v>
       </c>
       <c r="G3">
-        <v>-2.02419449410923</v>
+        <v>-4.038836913669329</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.42799156016522</v>
       </c>
       <c r="E4">
-        <v>-1.471470835337985</v>
+        <v>-6.113491800276669</v>
       </c>
       <c r="F4">
-        <v>-1.761227702137857</v>
+        <v>-1.928501588519967</v>
       </c>
       <c r="G4">
-        <v>-1.370709357384794</v>
+        <v>-4.082781095157614</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.01783721100713</v>
       </c>
       <c r="E5">
-        <v>-5.487289886022004</v>
+        <v>-5.849622148323725</v>
       </c>
       <c r="F5">
-        <v>-2.328949301646498</v>
+        <v>-2.195312102022465</v>
       </c>
       <c r="G5">
-        <v>-1.31490018068376</v>
+        <v>-2.825631221529235</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.46224878314831</v>
       </c>
       <c r="E6">
-        <v>-7.115040811131099</v>
+        <v>-6.899539790054082</v>
       </c>
       <c r="F6">
-        <v>-1.934679552610046</v>
+        <v>-1.943754317507714</v>
       </c>
       <c r="G6">
-        <v>-0.7561131991101767</v>
+        <v>-3.781389029262366</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.79036597973983</v>
       </c>
       <c r="E7">
-        <v>-5.678844336546461</v>
+        <v>-8.558863235944655</v>
       </c>
       <c r="F7">
-        <v>-2.306144347047428</v>
+        <v>-2.088038523359929</v>
       </c>
       <c r="G7">
-        <v>-0.009105150901329679</v>
+        <v>-3.686217466099397</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.02544524812187</v>
       </c>
       <c r="E8">
-        <v>-5.794193626469839</v>
+        <v>-9.396576585675579</v>
       </c>
       <c r="F8">
-        <v>-1.611902880639607</v>
+        <v>-2.137880561618973</v>
       </c>
       <c r="G8">
-        <v>-0.9321944952529326</v>
+        <v>-3.306378713105579</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.18298650989081</v>
       </c>
       <c r="E9">
-        <v>-8.513660008400089</v>
+        <v>-10.6163844582777</v>
       </c>
       <c r="F9">
-        <v>-2.450390447999114</v>
+        <v>-1.958232522973844</v>
       </c>
       <c r="G9">
-        <v>0.2031306130758068</v>
+        <v>-2.233305103097294</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.28562614951608</v>
       </c>
       <c r="E10">
-        <v>-6.509185330592898</v>
+        <v>-11.70905995158848</v>
       </c>
       <c r="F10">
-        <v>-1.256720475871652</v>
+        <v>-2.311911440905718</v>
       </c>
       <c r="G10">
-        <v>-0.2549926102851579</v>
+        <v>-2.143691945894763</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.35969484916733</v>
       </c>
       <c r="E11">
-        <v>-9.732539543830635</v>
+        <v>-13.00592433790511</v>
       </c>
       <c r="F11">
-        <v>-2.795394702488872</v>
+        <v>-2.385931866917673</v>
       </c>
       <c r="G11">
-        <v>1.18072808973151</v>
+        <v>-1.276848770255377</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.42653573306292</v>
       </c>
       <c r="E12">
-        <v>-9.94390153966464</v>
+        <v>-13.3717797529848</v>
       </c>
       <c r="F12">
-        <v>-1.911061141221426</v>
+        <v>-2.10713322036186</v>
       </c>
       <c r="G12">
-        <v>1.879041323603217</v>
+        <v>-1.856793448370443</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.49937306539769</v>
       </c>
       <c r="E13">
-        <v>-10.69355418384241</v>
+        <v>-13.60777211894653</v>
       </c>
       <c r="F13">
-        <v>-2.240591492626889</v>
+        <v>-2.411122519636806</v>
       </c>
       <c r="G13">
-        <v>1.758424907425411</v>
+        <v>0.2571852006410268</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.612130929176283</v>
       </c>
       <c r="E14">
-        <v>-12.44232404833248</v>
+        <v>-15.07321800714671</v>
       </c>
       <c r="F14">
-        <v>-2.047377281026113</v>
+        <v>-2.08251745462027</v>
       </c>
       <c r="G14">
-        <v>2.805159817123253</v>
+        <v>0.1927222579003382</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.788394111693833</v>
       </c>
       <c r="E15">
-        <v>-13.38973515242522</v>
+        <v>-16.95292869756857</v>
       </c>
       <c r="F15">
-        <v>-2.273520753622975</v>
+        <v>-1.801674397314349</v>
       </c>
       <c r="G15">
-        <v>2.799015444602366</v>
+        <v>1.563198726429049</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.041927387061516</v>
       </c>
       <c r="E16">
-        <v>-14.91316362181961</v>
+        <v>-16.48460750111733</v>
       </c>
       <c r="F16">
-        <v>-2.2134608034504</v>
+        <v>-2.216921722459296</v>
       </c>
       <c r="G16">
-        <v>4.295918336730304</v>
+        <v>1.573845440883346</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.390509107818684</v>
       </c>
       <c r="E17">
-        <v>-14.14426949158325</v>
+        <v>-18.29813454391709</v>
       </c>
       <c r="F17">
-        <v>-2.071201127530626</v>
+        <v>-2.229840112105954</v>
       </c>
       <c r="G17">
-        <v>5.5649894848456</v>
+        <v>2.331861053010269</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.847138276288306</v>
       </c>
       <c r="E18">
-        <v>-15.92421337114213</v>
+        <v>-18.65789010450845</v>
       </c>
       <c r="F18">
-        <v>-2.516492510007709</v>
+        <v>-2.104019387294737</v>
       </c>
       <c r="G18">
-        <v>6.61187005854717</v>
+        <v>3.080766043813119</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.412701360310599</v>
       </c>
       <c r="E19">
-        <v>-17.21099737431769</v>
+        <v>-20.1571501081239</v>
       </c>
       <c r="F19">
-        <v>-2.405473882317116</v>
+        <v>-1.987106925533226</v>
       </c>
       <c r="G19">
-        <v>7.075935711151127</v>
+        <v>3.635779003471933</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.076263598504251</v>
       </c>
       <c r="E20">
-        <v>-16.04112951307216</v>
+        <v>-21.0819867692884</v>
       </c>
       <c r="F20">
-        <v>-1.844932571455941</v>
+        <v>-1.653344445066861</v>
       </c>
       <c r="G20">
-        <v>7.991731923679715</v>
+        <v>3.282255776969781</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.835340317023102</v>
       </c>
       <c r="E21">
-        <v>-19.68238489315975</v>
+        <v>-20.90001004129017</v>
       </c>
       <c r="F21">
-        <v>-2.519882189419965</v>
+        <v>-1.393752325112357</v>
       </c>
       <c r="G21">
-        <v>6.555024681092345</v>
+        <v>5.069877536174358</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.678732318004176</v>
       </c>
       <c r="E22">
-        <v>-17.01945650921526</v>
+        <v>-21.66789432182281</v>
       </c>
       <c r="F22">
-        <v>-1.288397245354705</v>
+        <v>-1.162832486070953</v>
       </c>
       <c r="G22">
-        <v>7.983859446387328</v>
+        <v>4.992328006916931</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.588806385185265</v>
       </c>
       <c r="E23">
-        <v>-20.58471503850612</v>
+        <v>-23.60487662301968</v>
       </c>
       <c r="F23">
-        <v>-2.134925775093187</v>
+        <v>-1.796822649436152</v>
       </c>
       <c r="G23">
-        <v>8.243280415935697</v>
+        <v>5.256579062407096</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.553025631447125</v>
       </c>
       <c r="E24">
-        <v>-19.86497296514901</v>
+        <v>-22.63849574130882</v>
       </c>
       <c r="F24">
-        <v>-1.417415468340728</v>
+        <v>-1.326382032610076</v>
       </c>
       <c r="G24">
-        <v>7.680616785535626</v>
+        <v>5.128480813310537</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.561397764350057</v>
       </c>
       <c r="E25">
-        <v>-19.04180507393072</v>
+        <v>-23.95437066150966</v>
       </c>
       <c r="F25">
-        <v>-1.330914030670792</v>
+        <v>-1.210287169475128</v>
       </c>
       <c r="G25">
-        <v>7.384200469585902</v>
+        <v>5.455767966413965</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.604410908240646</v>
       </c>
       <c r="E26">
-        <v>-19.77064938004325</v>
+        <v>-24.2005837933067</v>
       </c>
       <c r="F26">
-        <v>-0.8251849624854577</v>
+        <v>-1.271314652774173</v>
       </c>
       <c r="G26">
-        <v>8.724090807877287</v>
+        <v>5.840109061341193</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.671722284909722</v>
       </c>
       <c r="E27">
-        <v>-19.32585813453586</v>
+        <v>-24.65308250157514</v>
       </c>
       <c r="F27">
-        <v>-1.392289428279013</v>
+        <v>-1.458640000508448</v>
       </c>
       <c r="G27">
-        <v>7.364668250904202</v>
+        <v>5.319390042923688</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.759539613458728</v>
       </c>
       <c r="E28">
-        <v>-21.07964101975243</v>
+        <v>-23.90246529243374</v>
       </c>
       <c r="F28">
-        <v>-0.5079384712961086</v>
+        <v>-1.132450454838476</v>
       </c>
       <c r="G28">
-        <v>8.019808660398274</v>
+        <v>5.504168142198109</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.868211065261675</v>
       </c>
       <c r="E29">
-        <v>-20.30653993716294</v>
+        <v>-23.92376723416582</v>
       </c>
       <c r="F29">
-        <v>-0.9226042825242907</v>
+        <v>-1.341742449360187</v>
       </c>
       <c r="G29">
-        <v>8.295514203454317</v>
+        <v>5.476207274573425</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.995941674352051</v>
       </c>
       <c r="E30">
-        <v>-20.01482017006283</v>
+        <v>-24.30703463180501</v>
       </c>
       <c r="F30">
-        <v>-1.14107707297123</v>
+        <v>-1.499299586107459</v>
       </c>
       <c r="G30">
-        <v>7.161215364242752</v>
+        <v>5.502108982872683</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.14251958350712</v>
       </c>
       <c r="E31">
-        <v>-21.16454537892224</v>
+        <v>-22.28431473222091</v>
       </c>
       <c r="F31">
-        <v>-1.138139682160902</v>
+        <v>-1.113463445598908</v>
       </c>
       <c r="G31">
-        <v>7.771885215507794</v>
+        <v>5.233411864723276</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.311751359287444</v>
       </c>
       <c r="E32">
-        <v>-20.64056470844271</v>
+        <v>-22.15792049419282</v>
       </c>
       <c r="F32">
-        <v>-1.71172198104435</v>
+        <v>-1.071321910716289</v>
       </c>
       <c r="G32">
-        <v>7.930592768660454</v>
+        <v>5.50725357064071</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.508103409092588</v>
       </c>
       <c r="E33">
-        <v>-17.82234136535319</v>
+        <v>-21.80559163097405</v>
       </c>
       <c r="F33">
-        <v>-0.2060457699176484</v>
+        <v>-1.529399144055582</v>
       </c>
       <c r="G33">
-        <v>6.594416862464132</v>
+        <v>5.293974984818703</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.731355635407933</v>
       </c>
       <c r="E34">
-        <v>-20.2744013571305</v>
+        <v>-21.61641915777762</v>
       </c>
       <c r="F34">
-        <v>-1.979292935822619</v>
+        <v>-1.299576891822887</v>
       </c>
       <c r="G34">
-        <v>6.901373955410896</v>
+        <v>4.798939178694865</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.980183968388946</v>
       </c>
       <c r="E35">
-        <v>-17.37789881234439</v>
+        <v>-20.43191979701331</v>
       </c>
       <c r="F35">
-        <v>-1.406156298601877</v>
+        <v>-1.003065265093012</v>
       </c>
       <c r="G35">
-        <v>7.047739794793154</v>
+        <v>4.768147794634103</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.257726912663867</v>
       </c>
       <c r="E36">
-        <v>-15.44676277109142</v>
+        <v>-20.69595700250454</v>
       </c>
       <c r="F36">
-        <v>-1.433692887805738</v>
+        <v>-1.212363886553947</v>
       </c>
       <c r="G36">
-        <v>5.72246882560319</v>
+        <v>4.442966148493651</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.56030656651491</v>
       </c>
       <c r="E37">
-        <v>-17.38737237996844</v>
+        <v>-20.02384541876011</v>
       </c>
       <c r="F37">
-        <v>-1.309650667808332</v>
+        <v>-1.530601105157044</v>
       </c>
       <c r="G37">
-        <v>6.010108885328307</v>
+        <v>4.496388421860871</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.880440550704864</v>
       </c>
       <c r="E38">
-        <v>-16.75474456109689</v>
+        <v>-19.39804201021812</v>
       </c>
       <c r="F38">
-        <v>-0.9205590434067787</v>
+        <v>-1.010360696809468</v>
       </c>
       <c r="G38">
-        <v>6.758967528493606</v>
+        <v>3.993543038809892</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.21504082212307</v>
       </c>
       <c r="E39">
-        <v>-16.21783056885146</v>
+        <v>-17.59638862626647</v>
       </c>
       <c r="F39">
-        <v>-1.043666036606425</v>
+        <v>-1.186930522185793</v>
       </c>
       <c r="G39">
-        <v>5.032660383221871</v>
+        <v>3.067841674027804</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.560562914203807</v>
       </c>
       <c r="E40">
-        <v>-15.04081224714782</v>
+        <v>-17.15649266116137</v>
       </c>
       <c r="F40">
-        <v>-1.047234643377685</v>
+        <v>-1.378757218386881</v>
       </c>
       <c r="G40">
-        <v>4.956825716553786</v>
+        <v>2.960176111999626</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.908103774588449</v>
       </c>
       <c r="E41">
-        <v>-14.53917053894814</v>
+        <v>-16.55858918098064</v>
       </c>
       <c r="F41">
-        <v>-0.5729611705788558</v>
+        <v>-1.187420915688251</v>
       </c>
       <c r="G41">
-        <v>5.457006110445652</v>
+        <v>2.305118466144036</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.248367381924183</v>
       </c>
       <c r="E42">
-        <v>-13.45960497788956</v>
+        <v>-15.38391660881297</v>
       </c>
       <c r="F42">
-        <v>-0.7354015331656305</v>
+        <v>-0.8106413159945067</v>
       </c>
       <c r="G42">
-        <v>3.8019981844532</v>
+        <v>2.639953663077003</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.580071797253712</v>
       </c>
       <c r="E43">
-        <v>-11.52551637158359</v>
+        <v>-15.35947643459357</v>
       </c>
       <c r="F43">
-        <v>-0.4166242190159079</v>
+        <v>-0.8039514208494979</v>
       </c>
       <c r="G43">
-        <v>4.526570665542407</v>
+        <v>1.857145375406477</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.896541107262024</v>
       </c>
       <c r="E44">
-        <v>-11.33549707374773</v>
+        <v>-14.27344421265205</v>
       </c>
       <c r="F44">
-        <v>0.1173538343396954</v>
+        <v>-0.5906724940181121</v>
       </c>
       <c r="G44">
-        <v>4.235110236264971</v>
+        <v>1.681722877826036</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.19035496333584</v>
       </c>
       <c r="E45">
-        <v>-8.941890624461429</v>
+        <v>-13.01201513544543</v>
       </c>
       <c r="F45">
-        <v>-0.400403128534288</v>
+        <v>-0.7980053996322031</v>
       </c>
       <c r="G45">
-        <v>3.861856158348763</v>
+        <v>1.187892110278493</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.46210801981212</v>
       </c>
       <c r="E46">
-        <v>-9.757577476619044</v>
+        <v>-12.19562184134262</v>
       </c>
       <c r="F46">
-        <v>-0.0005236754460770397</v>
+        <v>-0.3821450826091841</v>
       </c>
       <c r="G46">
-        <v>2.963271472078845</v>
+        <v>1.406868144973585</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.71231583918474</v>
       </c>
       <c r="E47">
-        <v>-7.590725306318816</v>
+        <v>-11.26923191359349</v>
       </c>
       <c r="F47">
-        <v>-0.2385765861929878</v>
+        <v>-0.4176108045926421</v>
       </c>
       <c r="G47">
-        <v>0.7963638209855072</v>
+        <v>0.4746251422058976</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.93780307672776</v>
       </c>
       <c r="E48">
-        <v>-5.289495198314978</v>
+        <v>-9.894369090968743</v>
       </c>
       <c r="F48">
-        <v>-0.0372841356801107</v>
+        <v>-0.3808950761983596</v>
       </c>
       <c r="G48">
-        <v>1.862243615536955</v>
+        <v>0.1659763604885663</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.13734127848005</v>
       </c>
       <c r="E49">
-        <v>-5.853892499312958</v>
+        <v>-9.626188331760495</v>
       </c>
       <c r="F49">
-        <v>0.15514726872502</v>
+        <v>-0.1712228610387628</v>
       </c>
       <c r="G49">
-        <v>1.078107799105182</v>
+        <v>-0.8972881030868571</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.31653341297845</v>
       </c>
       <c r="E50">
-        <v>-5.311503581992256</v>
+        <v>-9.550789239532785</v>
       </c>
       <c r="F50">
-        <v>0.2237427166160415</v>
+        <v>-0.2855872646692625</v>
       </c>
       <c r="G50">
-        <v>1.150307486771147</v>
+        <v>-0.2237245076667415</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.47341404913736</v>
       </c>
       <c r="E51">
-        <v>-3.188034192685511</v>
+        <v>-8.407992595905109</v>
       </c>
       <c r="F51">
-        <v>-0.202692538671116</v>
+        <v>0.3546819236091566</v>
       </c>
       <c r="G51">
-        <v>-0.5751620904791529</v>
+        <v>-1.593879853278143</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.60582162901493</v>
       </c>
       <c r="E52">
-        <v>-2.981884470434333</v>
+        <v>-7.829724579021635</v>
       </c>
       <c r="F52">
-        <v>0.3011006348938761</v>
+        <v>0.5369103267140058</v>
       </c>
       <c r="G52">
-        <v>-0.8067380614967117</v>
+        <v>-1.651804468578771</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.71737436102629</v>
       </c>
       <c r="E53">
-        <v>-2.94625896541599</v>
+        <v>-6.671771132890286</v>
       </c>
       <c r="F53">
-        <v>0.5326881380619367</v>
+        <v>0.2561848975792814</v>
       </c>
       <c r="G53">
-        <v>-0.7734604577359577</v>
+        <v>-2.422135310111784</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.80840190283942</v>
       </c>
       <c r="E54">
-        <v>-2.04244800906911</v>
+        <v>-5.870018395254272</v>
       </c>
       <c r="F54">
-        <v>0.4651447167724707</v>
+        <v>-0.1194233906069041</v>
       </c>
       <c r="G54">
-        <v>-0.6385623481017354</v>
+        <v>-3.068343867740902</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.87465967926478</v>
       </c>
       <c r="E55">
-        <v>-1.494407556186835</v>
+        <v>-4.961334800875139</v>
       </c>
       <c r="F55">
-        <v>1.042247577117816</v>
+        <v>0.2991100680249489</v>
       </c>
       <c r="G55">
-        <v>-0.8674004979583169</v>
+        <v>-2.869797209568651</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.91512228136756</v>
       </c>
       <c r="E56">
-        <v>-0.08785900093041457</v>
+        <v>-4.775160177471794</v>
       </c>
       <c r="F56">
-        <v>0.3852130609741379</v>
+        <v>0.07852659743567698</v>
       </c>
       <c r="G56">
-        <v>-1.691249618679187</v>
+        <v>-3.184140129613529</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.93182417973057</v>
       </c>
       <c r="E57">
-        <v>2.747273664103751</v>
+        <v>-3.946132440887582</v>
       </c>
       <c r="F57">
-        <v>0.5285570698241756</v>
+        <v>0.5408152506508027</v>
       </c>
       <c r="G57">
-        <v>-2.253962907262347</v>
+        <v>-3.154659721586319</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.91899625588541</v>
       </c>
       <c r="E58">
-        <v>0.7388456284878628</v>
+        <v>-2.965287613196221</v>
       </c>
       <c r="F58">
-        <v>0.5418142617385788</v>
+        <v>0.4702988187526891</v>
       </c>
       <c r="G58">
-        <v>-3.015093742741725</v>
+        <v>-3.108891429505895</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.87455262155347</v>
       </c>
       <c r="E59">
-        <v>2.962349008624047</v>
+        <v>-3.235605812136088</v>
       </c>
       <c r="F59">
-        <v>1.168232318674787</v>
+        <v>0.2624092502439168</v>
       </c>
       <c r="G59">
-        <v>-2.571517056480317</v>
+        <v>-4.043541198880633</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.8018739653661</v>
       </c>
       <c r="E60">
-        <v>2.909306992572204</v>
+        <v>-1.665366506924407</v>
       </c>
       <c r="F60">
-        <v>0.8107304851789936</v>
+        <v>0.2624109069787224</v>
       </c>
       <c r="G60">
-        <v>-2.346085457983646</v>
+        <v>-4.50578605143799</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.7009450463011</v>
       </c>
       <c r="E61">
-        <v>0.5720936301034173</v>
+        <v>-1.893465742690762</v>
       </c>
       <c r="F61">
-        <v>0.6752360858378841</v>
+        <v>0.2724995935774176</v>
       </c>
       <c r="G61">
-        <v>-2.176572284190804</v>
+        <v>-4.637704670086869</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.56999967747414</v>
       </c>
       <c r="E62">
-        <v>4.31574686445244</v>
+        <v>-1.346829116750866</v>
       </c>
       <c r="F62">
-        <v>0.04750920840525229</v>
+        <v>0.05770641113371421</v>
       </c>
       <c r="G62">
-        <v>-2.445007869242608</v>
+        <v>-3.352057620456443</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.41396601308024</v>
       </c>
       <c r="E63">
-        <v>3.043571718425622</v>
+        <v>-1.399748864004502</v>
       </c>
       <c r="F63">
-        <v>-0.4867968784418596</v>
+        <v>0.5845066609440598</v>
       </c>
       <c r="G63">
-        <v>-2.645855356564652</v>
+        <v>-4.249933849980956</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.23827166849141</v>
       </c>
       <c r="E64">
-        <v>4.310484777655527</v>
+        <v>-0.6351341417053926</v>
       </c>
       <c r="F64">
-        <v>0.2447443153792174</v>
+        <v>0.1545177094988924</v>
       </c>
       <c r="G64">
-        <v>-3.621036134976687</v>
+        <v>-3.4162060613709</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.04022944136376</v>
       </c>
       <c r="E65">
-        <v>2.432445094142492</v>
+        <v>-0.3240596766964928</v>
       </c>
       <c r="F65">
-        <v>-0.3979155412236811</v>
+        <v>-0.1305268272740286</v>
       </c>
       <c r="G65">
-        <v>-2.025071788677137</v>
+        <v>-4.682357308320558</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.82298497166924</v>
       </c>
       <c r="E66">
-        <v>5.218520800251564</v>
+        <v>-1.151389235527829</v>
       </c>
       <c r="F66">
-        <v>0.08835103483287912</v>
+        <v>-0.003615970960727594</v>
       </c>
       <c r="G66">
-        <v>-2.690120660970247</v>
+        <v>-4.644769374267673</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.59055160997005</v>
       </c>
       <c r="E67">
-        <v>4.9968519975761</v>
+        <v>-0.6371447841647983</v>
       </c>
       <c r="F67">
-        <v>0.1063928768658523</v>
+        <v>-0.1806977273919835</v>
       </c>
       <c r="G67">
-        <v>-0.7784362076814823</v>
+        <v>-3.875335690575803</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.34045141559954</v>
       </c>
       <c r="E68">
-        <v>6.001489427703762</v>
+        <v>-0.6206475533548551</v>
       </c>
       <c r="F68">
-        <v>0.2605106321567004</v>
+        <v>-0.08343248369007115</v>
       </c>
       <c r="G68">
-        <v>0.02496698378884938</v>
+        <v>-2.944473185297992</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.06869316182121</v>
       </c>
       <c r="E69">
-        <v>3.142256224000775</v>
+        <v>-1.688081332546881</v>
       </c>
       <c r="F69">
-        <v>-0.255899405320331</v>
+        <v>0.07901367746852309</v>
       </c>
       <c r="G69">
-        <v>-1.87252516077306</v>
+        <v>-2.546380084200631</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.776520253210878</v>
       </c>
       <c r="E70">
-        <v>3.702623183131928</v>
+        <v>-0.1161257356862929</v>
       </c>
       <c r="F70">
-        <v>-0.04658752998095195</v>
+        <v>-0.4748352531454348</v>
       </c>
       <c r="G70">
-        <v>-2.073015109176862</v>
+        <v>-3.103001968991532</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.461884190276299</v>
       </c>
       <c r="E71">
-        <v>4.833876746514052</v>
+        <v>-1.203231205967639</v>
       </c>
       <c r="F71">
-        <v>-0.03994485177790271</v>
+        <v>-0.3462751173331599</v>
       </c>
       <c r="G71">
-        <v>-0.8706713169511169</v>
+        <v>-2.519571286423613</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.116049011080126</v>
       </c>
       <c r="E72">
-        <v>2.295648951318786</v>
+        <v>-1.209408044514101</v>
       </c>
       <c r="F72">
-        <v>-0.1820173166646431</v>
+        <v>-0.1365175803310747</v>
       </c>
       <c r="G72">
-        <v>-0.9485519007624715</v>
+        <v>-1.521733134340806</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.740137008462606</v>
       </c>
       <c r="E73">
-        <v>2.60636566688108</v>
+        <v>-0.4783538430858372</v>
       </c>
       <c r="F73">
-        <v>-0.4535180464017923</v>
+        <v>-0.1058886956125629</v>
       </c>
       <c r="G73">
-        <v>-0.274978373705738</v>
+        <v>-1.811786581764051</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.334133492631107</v>
       </c>
       <c r="E74">
-        <v>2.744266757362658</v>
+        <v>-2.100136239452822</v>
       </c>
       <c r="F74">
-        <v>-1.085622017190817</v>
+        <v>0.1433281226218767</v>
       </c>
       <c r="G74">
-        <v>0.6607605651514201</v>
+        <v>-0.8896705378009941</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.893853368613756</v>
       </c>
       <c r="E75">
-        <v>2.165369282592117</v>
+        <v>-1.683466817533065</v>
       </c>
       <c r="F75">
-        <v>-0.4964026268447227</v>
+        <v>-0.162049520420161</v>
       </c>
       <c r="G75">
-        <v>0.8558112872342</v>
+        <v>-0.4992479707181253</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.41882524513113</v>
       </c>
       <c r="E76">
-        <v>4.14414487040578</v>
+        <v>-2.720233770745147</v>
       </c>
       <c r="F76">
-        <v>-0.4654945823114675</v>
+        <v>-0.6442015955870161</v>
       </c>
       <c r="G76">
-        <v>1.957084124145996</v>
+        <v>-0.4253731470092887</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.915683539284242</v>
       </c>
       <c r="E77">
-        <v>0.1743170017436608</v>
+        <v>-2.252659772505168</v>
       </c>
       <c r="F77">
-        <v>-0.5348496431108561</v>
+        <v>-0.7422239670950872</v>
       </c>
       <c r="G77">
-        <v>1.9365322574382</v>
+        <v>-0.4821324502800932</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.388093986005333</v>
       </c>
       <c r="E78">
-        <v>0.3376500022523152</v>
+        <v>-3.501137414049847</v>
       </c>
       <c r="F78">
-        <v>-0.5349333082185389</v>
+        <v>-0.962109952331202</v>
       </c>
       <c r="G78">
-        <v>2.623291687377851</v>
+        <v>0.5464805331357787</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.837423030021917</v>
       </c>
       <c r="E79">
-        <v>0.5330627126313064</v>
+        <v>-3.711616357452357</v>
       </c>
       <c r="F79">
-        <v>-0.8076741039576789</v>
+        <v>-1.204896982785112</v>
       </c>
       <c r="G79">
-        <v>3.672946498241331</v>
+        <v>0.6677954744223714</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.278006118640706</v>
       </c>
       <c r="E80">
-        <v>-0.03097231044605954</v>
+        <v>-4.005613946978333</v>
       </c>
       <c r="F80">
-        <v>-1.288096547987489</v>
+        <v>-0.5401420824473422</v>
       </c>
       <c r="G80">
-        <v>5.64361494140329</v>
+        <v>1.014061985102441</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.721682740338538</v>
       </c>
       <c r="E81">
-        <v>-1.836810004380799</v>
+        <v>-4.683757458100976</v>
       </c>
       <c r="F81">
-        <v>-1.408188283840944</v>
+        <v>-1.545329477578819</v>
       </c>
       <c r="G81">
-        <v>5.289949361442949</v>
+        <v>1.984237218659098</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.17762643500227</v>
       </c>
       <c r="E82">
-        <v>-1.634758551106563</v>
+        <v>-6.155149232673229</v>
       </c>
       <c r="F82">
-        <v>-1.099621426298128</v>
+        <v>-1.511894912467025</v>
       </c>
       <c r="G82">
-        <v>4.596793957521426</v>
+        <v>2.39426814697107</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.658374156766841</v>
       </c>
       <c r="E83">
-        <v>-2.304954590345745</v>
+        <v>-6.271983862071123</v>
       </c>
       <c r="F83">
-        <v>-2.076562321361545</v>
+        <v>-1.551384843293284</v>
       </c>
       <c r="G83">
-        <v>6.206218981983653</v>
+        <v>2.54335194424107</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.179636536566391</v>
       </c>
       <c r="E84">
-        <v>-4.760868313503587</v>
+        <v>-7.240420670981468</v>
       </c>
       <c r="F84">
-        <v>-1.670027764559243</v>
+        <v>-1.415081957367042</v>
       </c>
       <c r="G84">
-        <v>4.661720376637613</v>
+        <v>3.254791491175987</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.752788709001598</v>
       </c>
       <c r="E85">
-        <v>-4.634895223558213</v>
+        <v>-9.786075163549313</v>
       </c>
       <c r="F85">
-        <v>-1.678052987957564</v>
+        <v>-1.765709169787002</v>
       </c>
       <c r="G85">
-        <v>5.886324277069418</v>
+        <v>4.078332731161705</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.385212858354439</v>
       </c>
       <c r="E86">
-        <v>-8.136392838821072</v>
+        <v>-9.143883207573564</v>
       </c>
       <c r="F86">
-        <v>-1.937935036503048</v>
+        <v>-2.075684251914578</v>
       </c>
       <c r="G86">
-        <v>5.740315976605402</v>
+        <v>4.537005505082189</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.089306193003576</v>
       </c>
       <c r="E87">
-        <v>-7.157096749240333</v>
+        <v>-11.38845304879343</v>
       </c>
       <c r="F87">
-        <v>-1.364564799674717</v>
+        <v>-2.224215497440945</v>
       </c>
       <c r="G87">
-        <v>7.638053101537217</v>
+        <v>4.954124311393741</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.874467803288977</v>
       </c>
       <c r="E88">
-        <v>-9.114837575288368</v>
+        <v>-11.54572242260581</v>
       </c>
       <c r="F88">
-        <v>-2.586705759436398</v>
+        <v>-1.95223348624277</v>
       </c>
       <c r="G88">
-        <v>6.75713348626485</v>
+        <v>4.656638689234832</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.745802318295501</v>
       </c>
       <c r="E89">
-        <v>-11.39587974616601</v>
+        <v>-13.96581138788898</v>
       </c>
       <c r="F89">
-        <v>-2.47443381186537</v>
+        <v>-2.32832554099219</v>
       </c>
       <c r="G89">
-        <v>7.745728595202012</v>
+        <v>5.626903307521049</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.707774540631615</v>
       </c>
       <c r="E90">
-        <v>-12.07660901594703</v>
+        <v>-14.22138034698586</v>
       </c>
       <c r="F90">
-        <v>-3.316699562949045</v>
+        <v>-2.711578831938812</v>
       </c>
       <c r="G90">
-        <v>6.895616916718104</v>
+        <v>5.464448216817933</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.764096532139062</v>
       </c>
       <c r="E91">
-        <v>-14.1297149761226</v>
+        <v>-16.72211237739762</v>
       </c>
       <c r="F91">
-        <v>-2.761188927325072</v>
+        <v>-2.376976386926008</v>
       </c>
       <c r="G91">
-        <v>8.211757401310756</v>
+        <v>5.042969422031161</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.918275579231146</v>
       </c>
       <c r="E92">
-        <v>-14.39734778997592</v>
+        <v>-18.37108373170665</v>
       </c>
       <c r="F92">
-        <v>-2.928392402477944</v>
+        <v>-2.734410294294772</v>
       </c>
       <c r="G92">
-        <v>6.201726571686862</v>
+        <v>5.45337775253461</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.169587836665084</v>
       </c>
       <c r="E93">
-        <v>-17.86221005051672</v>
+        <v>-20.15352280044376</v>
       </c>
       <c r="F93">
-        <v>-3.001326010457426</v>
+        <v>-2.48863699935377</v>
       </c>
       <c r="G93">
-        <v>6.768922338930195</v>
+        <v>5.28503982240821</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.513664617480098</v>
       </c>
       <c r="E94">
-        <v>-20.48650149422776</v>
+        <v>-22.83619533106169</v>
       </c>
       <c r="F94">
-        <v>-2.350861276185351</v>
+        <v>-2.994492807751733</v>
       </c>
       <c r="G94">
-        <v>7.53719733168332</v>
+        <v>5.264971295349148</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.948181461423812</v>
       </c>
       <c r="E95">
-        <v>-21.9781355476143</v>
+        <v>-23.57143837094705</v>
       </c>
       <c r="F95">
-        <v>-3.621745030662561</v>
+        <v>-3.120148687449793</v>
       </c>
       <c r="G95">
-        <v>5.867156218397038</v>
+        <v>3.81485634332773</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.47364731694034</v>
       </c>
       <c r="E96">
-        <v>-25.20848172471988</v>
+        <v>-25.79164049353164</v>
       </c>
       <c r="F96">
-        <v>-3.960983848028834</v>
+        <v>-3.219879980909839</v>
       </c>
       <c r="G96">
-        <v>5.939951804260072</v>
+        <v>4.247339391487039</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.070019637281582</v>
       </c>
       <c r="E97">
-        <v>-26.13154775254738</v>
+        <v>-29.35475705461687</v>
       </c>
       <c r="F97">
-        <v>-3.697110725336663</v>
+        <v>-3.172374767094093</v>
       </c>
       <c r="G97">
-        <v>5.180062423357921</v>
+        <v>4.721475723621458</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.745348159323143</v>
       </c>
       <c r="E98">
-        <v>-30.4861351510342</v>
+        <v>-31.12031170801638</v>
       </c>
       <c r="F98">
-        <v>-4.169830180887839</v>
+        <v>-3.870659494794979</v>
       </c>
       <c r="G98">
-        <v>5.021116510926433</v>
+        <v>3.484367892687826</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.462930823349893</v>
       </c>
       <c r="E99">
-        <v>-30.45543888997321</v>
+        <v>-33.37338828765965</v>
       </c>
       <c r="F99">
-        <v>-4.136007939831535</v>
+        <v>-3.771484035862211</v>
       </c>
       <c r="G99">
-        <v>4.384276797173452</v>
+        <v>3.593466920934508</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.255852944492569</v>
       </c>
       <c r="E100">
-        <v>-35.39710671576244</v>
+        <v>-35.83032544594322</v>
       </c>
       <c r="F100">
-        <v>-3.766734177174558</v>
+        <v>-3.833399529017057</v>
       </c>
       <c r="G100">
-        <v>3.020490941179608</v>
+        <v>1.624774873459493</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.035740699929798</v>
       </c>
       <c r="E101">
-        <v>-37.21135831440343</v>
+        <v>-38.7966480029796</v>
       </c>
       <c r="F101">
-        <v>-3.872605329824154</v>
+        <v>-4.029800470016403</v>
       </c>
       <c r="G101">
-        <v>3.042320678465562</v>
+        <v>2.354872655053743</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.915516810243139</v>
       </c>
       <c r="E102">
-        <v>-39.58258957361784</v>
+        <v>-41.0503291339029</v>
       </c>
       <c r="F102">
-        <v>-4.52923063247085</v>
+        <v>-4.583611295729832</v>
       </c>
       <c r="G102">
-        <v>2.373342188617337</v>
+        <v>0.8814944995278657</v>
       </c>
     </row>
   </sheetData>
